--- a/results/auto_Cape_Town_Sports_and_Recreation.xlsx
+++ b/results/auto_Cape_Town_Sports_and_Recreation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>DuckDuckGo</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -478,6 +481,9 @@
       <c r="H2" t="s">
         <v>21</v>
       </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">

--- a/results/auto_Cape_Town_Sports_and_Recreation.xlsx
+++ b/results/auto_Cape_Town_Sports_and_Recreation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -34,22 +34,22 @@
     <t>Website</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
     <t>Sent</t>
   </si>
   <si>
-    <t>WPA Club List - Western Province Athletics</t>
-  </si>
-  <si>
-    <t>PDFStandard presentation template (16:9 format) - static.pmg.org.za</t>
-  </si>
-  <si>
-    <t>WPA Clubs Resources - Western Province Athletics</t>
+    <t>Western Province Rugby Union</t>
+  </si>
+  <si>
+    <t>Western Province Cricket Association</t>
+  </si>
+  <si>
+    <t>Cape Town Cycle Tour Trust</t>
+  </si>
+  <si>
+    <t>Two Oceans Marathon</t>
+  </si>
+  <si>
+    <t>Cape Town Spurs FC</t>
   </si>
   <si>
     <t>Sports &amp; Recreation</t>
@@ -58,28 +58,19 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>daniel.phahla@gmail.com</t>
-  </si>
-  <si>
-    <t>LQaeD@H.z</t>
-  </si>
-  <si>
-    <t>info@wpathletics.co.za</t>
-  </si>
-  <si>
-    <t>https://wpa.org.za/wpa-club-list/</t>
-  </si>
-  <si>
-    <t>https://static.pmg.org.za/250708CCT_Presentation_to_Parliament_SC_on_ESCI_Sporting_Facility_Portfolio_July_2025_Final.pdf</t>
-  </si>
-  <si>
-    <t>https://wpa.org.za/wpa-clubs-resources/</t>
-  </si>
-  <si>
-    <t>Cape Town CBD</t>
-  </si>
-  <si>
-    <t>DuckDuckGo</t>
+    <t>info@wprugby.co.za</t>
+  </si>
+  <si>
+    <t>info@wpca.co.za</t>
+  </si>
+  <si>
+    <t>info@capetowncycletour.com</t>
+  </si>
+  <si>
+    <t>info@twooceansmarathon.org.za</t>
+  </si>
+  <si>
+    <t>info@capetownspurs.co.za</t>
   </si>
   <si>
     <t>Yes</t>
@@ -89,20 +80,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,19 +106,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -427,10 +405,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -452,16 +430,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -472,22 +444,13 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -498,19 +461,13 @@
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -521,22 +478,45 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/results/auto_Cape_Town_Sports_and_Recreation.xlsx
+++ b/results/auto_Cape_Town_Sports_and_Recreation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -461,9 +461,6 @@
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -478,9 +475,6 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -495,9 +489,6 @@
       <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -511,9 +502,6 @@
       </c>
       <c r="D6" t="s">
         <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/results/auto_Cape_Town_Sports_and_Recreation.xlsx
+++ b/results/auto_Cape_Town_Sports_and_Recreation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -461,6 +461,9 @@
       <c r="D3" t="s">
         <v>15</v>
       </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -475,6 +478,9 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -489,6 +495,9 @@
       <c r="D5" t="s">
         <v>17</v>
       </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -502,6 +511,9 @@
       </c>
       <c r="D6" t="s">
         <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/results/auto_Cape_Town_Sports_and_Recreation.xlsx
+++ b/results/auto_Cape_Town_Sports_and_Recreation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -37,19 +37,7 @@
     <t>Sent</t>
   </si>
   <si>
-    <t>Western Province Rugby Union</t>
-  </si>
-  <si>
-    <t>Western Province Cricket Association</t>
-  </si>
-  <si>
-    <t>Cape Town Cycle Tour Trust</t>
-  </si>
-  <si>
-    <t>Two Oceans Marathon</t>
-  </si>
-  <si>
-    <t>Cape Town Spurs FC</t>
+    <t>H.H. Beach Sailing Club</t>
   </si>
   <si>
     <t>Sports &amp; Recreation</t>
@@ -58,19 +46,7 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>info@wprugby.co.za</t>
-  </si>
-  <si>
-    <t>info@wpca.co.za</t>
-  </si>
-  <si>
-    <t>info@capetowncycletour.com</t>
-  </si>
-  <si>
-    <t>info@twooceansmarathon.org.za</t>
-  </si>
-  <si>
-    <t>info@capetownspurs.co.za</t>
+    <t>doretted@mweb.co.za</t>
   </si>
   <si>
     <t>Yes</t>
@@ -405,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -436,84 +412,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
